--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488234_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488234_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8664</v>
+        <v>3.1722</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2141</v>
+        <v>1.4214</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6523</v>
+        <v>1.7508</v>
       </c>
       <c r="G2" t="n">
         <v>2.4923</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7551</v>
+        <v>-0.4492</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7822</v>
+        <v>-0.5748</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0271</v>
+        <v>0.1256</v>
       </c>
       <c r="V2" t="n">
         <v>0.9439</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7417</v>
+        <v>1.2336</v>
       </c>
       <c r="E4" t="n">
-        <v>2.033</v>
+        <v>1.1778</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2913</v>
+        <v>0.0558</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5867</v>
+        <v>-0.9675</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3823</v>
+        <v>-0.8107</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2043</v>
+        <v>-0.1568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2037</v>
+        <v>-0.1036</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7938</v>
+        <v>-0.1463</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.59</v>
+        <v>0.0427</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7904</v>
+        <v>-0.864</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1761</v>
+        <v>-0.6644</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6143</v>
+        <v>-0.1996</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9752</v>
+        <v>-0.1694</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0707</v>
+        <v>-0.1246</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0955</v>
+        <v>-0.0448</v>
       </c>
       <c r="V4" t="n">
-        <v>0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9439</v>
+        <v>2.5177</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6291</v>
+        <v>0.1607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.524</v>
+        <v>1.3043</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1051</v>
+        <v>-1.1436</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9675</v>
+        <v>-2.5867</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8107</v>
+        <v>-1.3823</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1568</v>
+        <v>-1.2043</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1036</v>
+        <v>0.2037</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1463</v>
+        <v>0.7938</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0427</v>
+        <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.864</v>
+        <v>-2.7904</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6644</v>
+        <v>-2.1761</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1996</v>
+        <v>-0.6143</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R5" t="n">
         <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.774</v>
+        <v>0.3942</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7784</v>
+        <v>0.342</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0045</v>
+        <v>0.0522</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5177</v>
+        <v>0.9439</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>H. FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0445</v>
+        <v>-0.1912</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4363</v>
+        <v>-1.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3917</v>
+        <v>1.6087</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5596</v>
+        <v>-0.8873</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4136</v>
+        <v>0.0267</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8541</v>
+        <v>-0.914</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7894</v>
+        <v>-1.2413</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0429</v>
+        <v>0.0644</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7465000000000001</v>
+        <v>-1.3057</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.349</v>
+        <v>0.354</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4566</v>
+        <v>-0.0377</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1076</v>
+        <v>0.3917</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1033</v>
+        <v>-0.4156</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.5586</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3447</v>
+        <v>0.143</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. FERREIRA</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2892</v>
+        <v>-0.5936</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8979</v>
+        <v>-2.6836</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6087</v>
+        <v>2.09</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8873</v>
+        <v>0.3835</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0267</v>
+        <v>-0.3523</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.914</v>
+        <v>0.7358</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2413</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0644</v>
+        <v>-0.5844</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3057</v>
+        <v>0.0829</v>
       </c>
       <c r="M7" t="n">
-        <v>0.354</v>
+        <v>0.885</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0377</v>
+        <v>0.2322</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3917</v>
+        <v>0.6529</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R7" t="n">
         <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.0507</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6566</v>
+        <v>-0.1439</v>
       </c>
       <c r="U7" t="n">
-        <v>0.143</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8737</v>
+        <v>-0.6163</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0868</v>
+        <v>-0.2492</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2131</v>
+        <v>-0.3671</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3835</v>
+        <v>-0.5596</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3523</v>
+        <v>-1.4136</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7358</v>
+        <v>0.8541</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.7894</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5844</v>
+        <v>0.0429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0829</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.885</v>
+        <v>-1.349</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2322</v>
+        <v>-1.4566</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6529</v>
+        <v>0.1076</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3308</v>
+        <v>0.4424</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5471</v>
+        <v>0.0731</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2164</v>
+        <v>0.3693</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9087</v>
+        <v>-0.6828</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3186</v>
+        <v>-2.068</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4099</v>
+        <v>1.3853</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5246</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4964</v>
+        <v>-0.2705</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8207</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3243</v>
+        <v>0.2997</v>
       </c>
       <c r="V9" t="n">
         <v>0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3207</v>
+        <v>-1.9957</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6172</v>
+        <v>-2.4646</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2965</v>
+        <v>0.4688</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2356</v>
@@ -1234,13 +1234,13 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8998</v>
+        <v>-0.5748</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4924</v>
+        <v>-0.3398</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4074</v>
+        <v>-0.235</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7028</v>
+        <v>-2.875</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6027</v>
+        <v>-2.4896</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1</v>
+        <v>-0.3854</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.354</v>
+        <v>-2.209</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3433</v>
+        <v>-1.3225</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0107</v>
+        <v>-0.8865</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6726</v>
+        <v>-1.7133</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8385</v>
+        <v>-0.4811</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1659</v>
+        <v>-1.2322</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6814</v>
+        <v>-0.4957</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5048</v>
+        <v>-0.8414</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1766</v>
+        <v>0.3457</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0343</v>
+        <v>0.1116</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0037</v>
+        <v>0.0395</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0306</v>
+        <v>0.0721</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3144</v>
+        <v>-1.8894</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2525</v>
+        <v>-2.9473</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0887</v>
+        <v>-2.8965</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1638</v>
+        <v>-0.0508</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.209</v>
+        <v>-2.354</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3225</v>
+        <v>-2.3433</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8865</v>
+        <v>-0.0107</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7133</v>
+        <v>-1.6726</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4811</v>
+        <v>-1.8385</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2322</v>
+        <v>0.1659</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4957</v>
+        <v>-0.6814</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8414</v>
+        <v>-0.5048</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3457</v>
+        <v>-0.1766</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2659</v>
+        <v>-0.2789</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5596</v>
+        <v>-0.2975</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2937</v>
+        <v>0.0186</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8894</v>
+        <v>-0.3144</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8292</v>
+        <v>-3.739</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1993</v>
+        <v>-5.0352</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3701</v>
+        <v>1.2962</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3579</v>
@@ -1468,13 +1468,13 @@
         <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6387</v>
+        <v>-0.5484</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.3444</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1301</v>
+        <v>-0.204</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5738</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.0289</v>
+        <v>-7.2082</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.7376</v>
+        <v>-13.917</v>
       </c>
       <c r="F14" t="n">
-        <v>6.7089</v>
+        <v>6.7087</v>
       </c>
       <c r="G14" t="n">
         <v>-10.9402</v>
@@ -1522,13 +1522,13 @@
         <v>-3.445499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4347999999999996</v>
+        <v>0.4348000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.8801</v>
+        <v>-3.880099999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.4949</v>
+        <v>-7.494900000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-6.266900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>17.602</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6301</v>
+        <v>-1.8093</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.32</v>
+        <v>-2.4991</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6901</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9437000000000002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0726</v>
+        <v>3.1549</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4498</v>
+        <v>1.7355</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6228</v>
+        <v>1.4194</v>
       </c>
       <c r="G15" t="n">
-        <v>3.569</v>
+        <v>1.5553</v>
       </c>
       <c r="H15" t="n">
-        <v>3.36</v>
+        <v>1.0161</v>
       </c>
       <c r="I15" t="n">
-        <v>0.209</v>
+        <v>0.5391</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9102</v>
+        <v>1.7921</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8474</v>
+        <v>0.4851</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06279999999999999</v>
+        <v>1.307</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3412</v>
+        <v>-0.2368</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4874</v>
+        <v>0.531</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1462</v>
+        <v>-0.7678</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1162</v>
+        <v>-0.0864</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3656</v>
+        <v>-0.0566</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4818</v>
+        <v>-0.0299</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3155</v>
+        <v>0.945</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4718</v>
+        <v>2.5309</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9383</v>
+        <v>0.4498</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5335</v>
+        <v>2.0811</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5976</v>
+        <v>3.569</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3488</v>
+        <v>3.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2488</v>
+        <v>0.209</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3884</v>
+        <v>3.9102</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3778</v>
+        <v>3.8474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0107</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2092</v>
+        <v>-0.3412</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.029</v>
+        <v>-0.4874</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2381</v>
+        <v>0.1462</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7411</v>
+        <v>-1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3565</v>
+        <v>0.5745</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2174</v>
+        <v>-0.3656</v>
       </c>
       <c r="U16" t="n">
-        <v>0.139</v>
+        <v>0.9401</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2589</v>
+        <v>-0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2589</v>
+        <v>-0.3155</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4025</v>
+        <v>2.1878</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5397</v>
+        <v>0.7457</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8628</v>
+        <v>1.4421</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5553</v>
+        <v>2.5889</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0161</v>
+        <v>1.7763</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5391</v>
+        <v>0.8126</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7921</v>
+        <v>1.5122</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4851</v>
+        <v>1.46</v>
       </c>
       <c r="L17" t="n">
-        <v>1.307</v>
+        <v>0.0522</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2368</v>
+        <v>1.0767</v>
       </c>
       <c r="N17" t="n">
-        <v>0.531</v>
+        <v>0.3163</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7678</v>
+        <v>0.7604</v>
       </c>
       <c r="P17" t="n">
         <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8389</v>
+        <v>0.1166</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2524</v>
+        <v>-0.1545</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5865</v>
+        <v>0.2711</v>
       </c>
       <c r="V17" t="n">
-        <v>0.945</v>
+        <v>-1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>0.945</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1391</v>
+        <v>1.9248</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6478</v>
+        <v>1.1549</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4913</v>
+        <v>0.77</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5889</v>
+        <v>0.5976</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7763</v>
+        <v>0.3488</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8126</v>
+        <v>0.2488</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5122</v>
+        <v>0.3884</v>
       </c>
       <c r="K18" t="n">
-        <v>1.46</v>
+        <v>0.3778</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0522</v>
+        <v>0.0107</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0767</v>
+        <v>0.2092</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3163</v>
+        <v>-0.029</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7604</v>
+        <v>0.2381</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0679</v>
+        <v>0.8095</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2524</v>
+        <v>0.434</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3203</v>
+        <v>0.3755</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2589</v>
+        <v>1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9489</v>
+        <v>1.4275</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-1.373</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9573</v>
+        <v>2.8005</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1006</v>
+        <v>1.192</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0667</v>
+        <v>-1.109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0339</v>
+        <v>2.301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9283</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1711</v>
+        <v>-0.7522</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7572</v>
+        <v>1.3484</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1723</v>
+        <v>0.5958</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1044</v>
+        <v>-0.3568</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2767</v>
+        <v>0.9526</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8864</v>
+        <v>0.1063</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2137</v>
+        <v>-0.4309</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6727</v>
+        <v>0.5372</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6289</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. GARCÍA REYES</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3221</v>
+        <v>1.0824</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3221</v>
+        <v>-0.8898</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.9722</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3221</v>
+        <v>1.1006</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3221</v>
+        <v>0.0667</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.0339</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3221</v>
+        <v>0.9283</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3221</v>
+        <v>0.1711</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.7572</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.1723</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.1044</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.2767</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.6877</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2244</v>
+        <v>0.4417</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9606</v>
+        <v>-2.6699</v>
       </c>
       <c r="F22" t="n">
-        <v>2.185</v>
+        <v>3.1116</v>
       </c>
       <c r="G22" t="n">
-        <v>1.192</v>
+        <v>-0.2699</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.109</v>
+        <v>-1.0718</v>
       </c>
       <c r="I22" t="n">
-        <v>2.301</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5963000000000001</v>
+        <v>-1.4018</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7522</v>
+        <v>-0.7904</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3484</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5958</v>
+        <v>1.1319</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3568</v>
+        <v>-0.2814</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9526</v>
+        <v>1.4133</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0968</v>
+        <v>0.1558</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0184</v>
+        <v>-0.3416</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0784</v>
+        <v>0.4974</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0193</v>
+        <v>0.403</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5258</v>
+        <v>-0.4279</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5451</v>
+        <v>0.8309</v>
       </c>
       <c r="G23" t="n">
         <v>-0.216</v>
@@ -2248,13 +2248,13 @@
         <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>0.05</v>
+        <v>0.4337</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0211</v>
+        <v>0.1191</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0288</v>
+        <v>0.3146</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>I. GARCÍA REYES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1229</v>
+        <v>0.3221</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9637</v>
+        <v>0.3221</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8407</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2699</v>
+        <v>0.3221</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0718</v>
+        <v>0.3221</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8018999999999999</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4018</v>
+        <v>0.3221</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7904</v>
+        <v>0.3221</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1319</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2814</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4133</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4089</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6354</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2266</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4771</v>
+        <v>-1.2314</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6243</v>
+        <v>-1.5264</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1472</v>
+        <v>0.2949</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5185999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4027</v>
+        <v>-0.157</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2932</v>
+        <v>-0.1455</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5148</v>
+        <v>-1.4041</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.9548</v>
+        <v>-3.4651</v>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>2.061</v>
       </c>
       <c r="G26" t="n">
         <v>1.7114</v>
@@ -2482,13 +2482,13 @@
         <v>2.2234</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.849</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7784</v>
+        <v>-0.2888</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5168</v>
+        <v>1.1378</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6294</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7232</v>
+        <v>-2.7713</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8349</v>
+        <v>-2.0308</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8882</v>
+        <v>-0.7405</v>
       </c>
       <c r="G27" t="n">
         <v>-1.9586</v>
@@ -2560,13 +2560,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1619</v>
+        <v>0.1138</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2699</v>
+        <v>0.074</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1079</v>
+        <v>0.0398</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>8.028899999999998</v>
+        <v>9.334500000000002</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.708600000000001</v>
+        <v>-6.708700000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>14.7375</v>
+        <v>16.0432</v>
       </c>
       <c r="G28" t="n">
         <v>10.94</v>
       </c>
       <c r="H28" t="n">
-        <v>5.832199999999999</v>
+        <v>5.8322</v>
       </c>
       <c r="I28" t="n">
         <v>5.107900000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>7.4947</v>
+        <v>7.494700000000002</v>
       </c>
       <c r="K28" t="n">
-        <v>6.267</v>
+        <v>6.266999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>1.2278</v>
@@ -2638,13 +2638,13 @@
         <v>11.1172</v>
       </c>
       <c r="S28" t="n">
-        <v>2.63</v>
+        <v>3.9358</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6898999999999997</v>
+        <v>-0.6900000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>3.32</v>
+        <v>4.6258</v>
       </c>
       <c r="V28" t="n">
         <v>0.9439</v>
